--- a/artfynd/A 263-2023 artfynd.xlsx
+++ b/artfynd/A 263-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137284638</v>
       </c>
       <c r="B2" t="n">
-        <v>107865</v>
+        <v>107886</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Källshult O, Lohallavägen, Hl</t>
+          <t>Källshult SO, Lohallavägen, Hl</t>
         </is>
       </c>
       <c r="Q2" t="n">

--- a/artfynd/A 263-2023 artfynd.xlsx
+++ b/artfynd/A 263-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137284638</v>
       </c>
       <c r="B2" t="n">
-        <v>107886</v>
+        <v>107887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 263-2023 artfynd.xlsx
+++ b/artfynd/A 263-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137284638</v>
       </c>
       <c r="B2" t="n">
-        <v>107887</v>
+        <v>107892</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 263-2023 artfynd.xlsx
+++ b/artfynd/A 263-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137284638</v>
       </c>
       <c r="B2" t="n">
-        <v>107892</v>
+        <v>107895</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 263-2023 artfynd.xlsx
+++ b/artfynd/A 263-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137284638</v>
       </c>
       <c r="B2" t="n">
-        <v>107895</v>
+        <v>107901</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 263-2023 artfynd.xlsx
+++ b/artfynd/A 263-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137284638</v>
       </c>
       <c r="B2" t="n">
-        <v>107901</v>
+        <v>107902</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 263-2023 artfynd.xlsx
+++ b/artfynd/A 263-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137284638</v>
       </c>
       <c r="B2" t="n">
-        <v>107902</v>
+        <v>107914</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 263-2023 artfynd.xlsx
+++ b/artfynd/A 263-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137284638</v>
       </c>
       <c r="B2" t="n">
-        <v>107914</v>
+        <v>107915</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 263-2023 artfynd.xlsx
+++ b/artfynd/A 263-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137284638</v>
       </c>
       <c r="B2" t="n">
-        <v>107915</v>
+        <v>107918</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 263-2023 artfynd.xlsx
+++ b/artfynd/A 263-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137284638</v>
       </c>
       <c r="B2" t="n">
-        <v>107918</v>
+        <v>107924</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
